--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_768_Togo.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_768_Togo.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R1bbb5648ffab41c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R1bd5163f32544e2b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R1ccd9177843e4f00"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rcca218d4aca04e47"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R23fd7061e18c4eae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Ra50f95175e314dab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R4e5974b44bb340c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rbf648df1ce3242a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rbbd78817108e4c4e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rc207a1f6d9564fcb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R8b8c6e814e314981"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R2b99578aada44e41"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ768CommercialTable" displayName="EEZ768CommercialTable" ref="A1:O12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O12"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ768CommercialTable" displayName="EEZ768CommercialTable" ref="A1:E12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E12"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ768FunctionalTable" displayName="EEZ768FunctionalTable" ref="A1:O22" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O22"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ768FunctionalTable" displayName="EEZ768FunctionalTable" ref="A1:E22" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E22"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ768ValidationTable" displayName="EEZ768ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ768ValidationTable" displayName="EEZ768ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -9337,7 +9291,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R788544fe32994d7c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rafa1fa7c02f844be"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9347,20 +9301,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -9368,660 +9312,231 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>10815.040359124801</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.11</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>128.82495516931337</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>10815.040359124801</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$130,A2,'Species'!$U$2:$U$130))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>1393247.0894185673</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.11</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>1393247.0894185673</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>0.1457768539</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.91</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>812.8305161640995</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>0.1457768539</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>812.8305161640995</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$130,A3,'Species'!$U$2:$U$130))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>118.49187540031554</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.91</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>812.8305161640995</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>118.49187540031554</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>98.80890233109999</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.0528630380970743</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>112.94396711383766</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>98.80890233109999</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>166.23535001482134</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$130,A4,'Species'!$U$2:$U$130))</x:f>
-        <x:v>16425.5324635907</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.0528630380970743</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>112.94396711383766</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>11159.869415438154</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>5265.663048152548</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.4718391275141824</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.4718391275141825</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>72.3508794683</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.2166796891995317</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>164.69472492628188</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>72.3508794683</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>178.4968348310872</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$130,A5,'Species'!$U$2:$U$130))</x:f>
-        <x:v>12914.402982337042</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.2166796891995317</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>164.69472492628188</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>11915.808192206243</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>998.5947901307991</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.083804201445937</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.08380420144593706</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>2101.7277981306</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.392066140445472</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>246.6414928837953</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>2101.7277981306</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>252.83846489605963</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$130,A6,'Species'!$U$2:$U$130))</x:f>
-        <x:v>531397.6301087164</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.392066140445472</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>246.6414928837953</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>518373.2817663032</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>13024.348342413257</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0251254237063185</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.025125423706318623</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>0.15182094540000002</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>2.451055907303025</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>28.252436488584912</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>0.15182094540000002</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>48.31115648501586</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$130,A7,'Species'!$U$2:$U$130))</x:f>
-        <x:v>7.33464545092245</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>2.451055907303025</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>28.252436488584912</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>4.2893116175504185</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>3.0453338333720312</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.7099819516286834</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.7099819516286835</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>22858.606474337194</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.281495754777826</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>191.20346344027521</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>22858.606474337194</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>193.65445842438572</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$130,A8,'Species'!$U$2:$U$130))</x:f>
-        <x:v>4426671.0571239265</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.281495754777826</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>191.20346344027521</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>4370644.72731157</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>56026.32981235627</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0128187792208905</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.01281877922089052</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>11541.781238460699</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.4224055859489235</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>264.48776453764435</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>11541.781238460699</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>463.15589896925735</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$130,A9,'Species'!$U$2:$U$130))</x:f>
-        <x:v>5345644.065205773</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.4224055859489235</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>264.48776453764435</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>3052659.9185429947</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>2292984.1466627787</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.7511430057224318</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.7511430057224318</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>4.7970208184</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.732875437808627</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>540.599248709983</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>4.7970208184</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>552.3341415412376</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$130,A10,'Species'!$U$2:$U$130))</x:f>
-        <x:v>2649.5583756864094</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.732875437808627</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>540.599248709983</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>2593.265850473188</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>56.292525213221325</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0217071941170048</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.021707194117004912</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>281.3100366004999</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.258872518502768</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>1814.9828199691851</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>281.3100366004999</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>2035.6011046544163</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$130,A11,'Species'!$U$2:$U$130))</x:f>
-        <x:v>572635.021254352</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.258872518502768</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>1814.9828199691851</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>510572.88351481006</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>62062.13773954188</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.1215539245098622</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.12155392450986219</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>3559.7914707369996</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.437237215387548</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>2736.7631617495035</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>3559.7914707369996</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>2748.515897303571</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$H$2:$H$130,A12,'Species'!$U$2:$U$130))</x:f>
-        <x:v>9784143.448406303</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.437237215387548</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>2736.7631617495035</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>9742306.160623107</x:v>
       </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>41837.287783196196</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.004294392630802</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.004294392630801939</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G12">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O12">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfe7c775b265f4aec"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc055e5559e4d4f8b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10031,20 +9546,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -10052,1200 +9557,421 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>30.6057242767</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.7167727084827336</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>520.9220110186142</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>30.6057242767</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>536.4415648201766</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$130,A2,'Species'!$U$2:$U$130))</x:f>
-        <x:v>16418.182623447814</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.7167727084827336</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>520.9220110186142</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>15943.195438899784</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>474.9871845480302</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0297924707984893</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.02979247079848934</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>989.5310076192999</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.972781053316589</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>939.2496746887867</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>989.5310076192999</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>959.6475209816708</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$130,A3,'Species'!$U$2:$U$130))</x:f>
-        <x:v>949600.978396356</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.972781053316589</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>939.2496746887867</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>929416.6770008948</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>20184.301395461196</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0217171715280526</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.021717171528052713</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>420.68270660850004</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.909820816705985</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>812.4952238360305</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>420.68270660850004</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>840.6228263000999</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$130,A4,'Species'!$U$2:$U$130))</x:f>
-        <x:v>353635.485804813</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.909820816705985</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>812.4952238360305</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>341802.6898698204</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>11832.79593499261</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.034618791149652</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.03461879114965207</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>3458.0621996956</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.440032489920361</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>2754.4347571156127</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>3458.0621996956</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>2761.5190763808846</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$130,A5,'Species'!$U$2:$U$130))</x:f>
-        <x:v>9549504.731771044</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.440032489920361</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>2754.4347571156127</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>9525006.715109231</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>24498.016661813483</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0025719684399752</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.0025719684399752724</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>35.2472767693</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.61</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>407.3802778041126</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>35.2472767693</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>407.3802778041126</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$130,A6,'Species'!$U$2:$U$130))</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>14359.045402115878</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.61</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>407.3802778041126</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
-        <x:v>14359.045402115878</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>690.7339718571</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.5663755250769857</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>368.4474244897174</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>690.7339718571</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>374.2546813508064</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$130,A7,'Species'!$U$2:$U$130))</x:f>
-        <x:v>258510.42253555582</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.5663755250769857</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>368.4474244897174</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>254499.1529383014</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>4011.2695972544025</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0157614261224157</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.015761426122415663</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>243.92091228680002</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.356665790924446</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>2273.3473147771165</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>243.92091228680002</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>2283.2177700225766</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$130,A8,'Species'!$U$2:$U$130))</x:f>
-        <x:v>556924.56141334</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.356665790924446</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>2273.3473147771165</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>554516.9509651813</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>2407.6104481586954</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0043418157803257</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.0043418157803256615</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>2.0842346429</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>2.6335445693915354</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>43.007536777159814</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>2.0842346429</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>49.0796378254893</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$130,A9,'Species'!$U$2:$U$130))</x:f>
-        <x:v>102.29348141687001</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>2.6335445693915354</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>43.007536777159814</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>89.63779805675229</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>12.65568336011772</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.1411869059088784</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.1411869059088783</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>12.487901667400001</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.390628242676549</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>2458.262423563151</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>12.487901667400001</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>2692.7231771039037</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$130,A10,'Species'!$U$2:$U$130))</x:f>
-        <x:v>33626.462253202466</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.390628242676549</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>2458.262423563151</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>30698.539418121043</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>2927.922835081423</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.095376616952437</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.09537661695243713</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium bathypelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>60.7834057966</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.08</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>1202.2644346174131</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>60.7834057966</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>1202.2644346174131</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$130,A11,'Species'!$U$2:$U$130))</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>73077.7270041701</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.08</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>1202.2644346174131</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
-        <x:v>73077.7270041701</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>209.58402513289997</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.5282761927015014</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>337.5018771713218</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>209.58402513289997</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>408.12913632894094</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$130,A12,'Species'!$U$2:$U$130))</x:f>
-        <x:v>85537.34716583352</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.5282761927015014</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>337.5018771713218</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>70735.00190747522</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>14802.345258358298</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.2092647891311359</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.20926478913113591</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>24290.383740579597</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.292918803902127</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>196.2993239495311</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>24290.383740579597</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>199.01446799253534</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$130,A13,'Species'!$U$2:$U$130))</x:f>
-        <x:v>4834137.797465979</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.292918803902127</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>196.2993239495311</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>4768185.906750457</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>65951.89071552176</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.0138316525415152</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.013831652541515166</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>2935.3104247704</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.826528655347143</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>670.7005389862353</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>2935.3104247704</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>830.6814399719466</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$130,A14,'Species'!$U$2:$U$130))</x:f>
-        <x:v>2438307.890412942</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.826528655347143</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>670.7005389862353</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>1968714.2839854225</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>469593.6064275196</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.2385280638472762</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.23852806384727623</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>1173.7989318131001</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.6270452380946248</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>423.6870969320761</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>1173.7989318131001</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>535.3502935574826</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$130,A15,'Species'!$U$2:$U$130))</x:f>
-        <x:v>628393.6027236027</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.6270452380946248</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>423.6870969320761</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>497323.4618018643</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>131070.14092173835</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.2635510909677476</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.2635510909677477</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>0.15182094540000002</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>2.451055907303025</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>28.252436488584912</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>0.15182094540000002</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>48.31115648501586</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$130,A16,'Species'!$U$2:$U$130))</x:f>
-        <x:v>7.33464545092245</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>2.451055907303025</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>28.252436488584912</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>4.2893116175504185</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>3.0453338333720312</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.7099819516286834</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.7099819516286835</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>96.72466768820001</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.0618985623306756</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>115.31838785130732</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>96.72466768820001</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>168.75983523451478</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$130,A17,'Species'!$U$2:$U$130))</x:f>
-        <x:v>16323.23898217383</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.0618985623306756</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>115.31838785130732</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>11154.132743256663</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>5169.1062389171675</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.4634252037247988</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.46342520372479873</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>27.5675145508</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.27</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>186.20871366628674</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>27.5675145508</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>186.20871366628674</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$130,A18,'Species'!$U$2:$U$130))</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>5133.31142348111</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.27</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>186.20871366628674</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
-        <x:v>5133.31142348111</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>3795.4890861785</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>2.8050595757391847</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>63.83510480380745</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>3795.4890861785</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>98.31566885736413</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$130,A19,'Species'!$U$2:$U$130))</x:f>
-        <x:v>373156.048148465</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>2.8050595757391847</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>63.83510480380745</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>242285.44359791192</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>130870.60455055308</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.5401505043272066</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.5401505043272066</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>12786.869497916101</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.1538099433939872</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>142.4983853548488</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>12786.869497916101</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>147.40365912803378</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$130,A20,'Species'!$U$2:$U$130))</x:f>
-        <x:v>1884831.3527854774</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.1538099433939872</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>142.4983853548488</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>1822108.2571962106</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>62723.09558926686</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1.0344233638926497</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0.034423363892649675</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>72.3508794683</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>3.2166796891995317</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>164.69472492628188</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>72.3508794683</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>178.4968348310872</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$130,A21,'Species'!$U$2:$U$130))</x:f>
-        <x:v>12914.402982337042</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>3.2166796891995317</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>164.69472492628188</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>11915.808192206243</x:v>
-      </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>998.5947901307991</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1.083804201445937</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0.08380420144593706</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="18" customHeight="1">
       <x:c r="A22" s="24" t="str">
         <x:v>Small to medium rays (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B22" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C22" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D22" s="31" t="n">
+      <x:c r="B22" s="31" t="n">
         <x:v>2.1418475444</x:v>
       </x:c>
+      <x:c r="C22" s="32" t="n">
+        <x:v>3.8000000000000003</x:v>
+      </x:c>
+      <x:c r="D22" s="32" t="n">
+        <x:f>IF(C22="","",(1/'Metadata'!$B$5)^(C22-1))</x:f>
+        <x:v>630.9573444801937</x:v>
+      </x:c>
       <x:c r="E22" s="31" t="n">
-        <x:v>2.1418475444</x:v>
-      </x:c>
-      <x:c r="F22" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H22" s="32" t="n">
-        <x:f>IF(E22=0,"",I22/E22)</x:f>
-        <x:v>630.957344480193</x:v>
-      </x:c>
-      <x:c r="I22" s="31" t="n">
-        <x:f>IF(C22=0,"",SUMIF('Species'!$G$2:$G$130,A22,'Species'!$U$2:$U$130))</x:f>
-        <x:v>1351.4144388960462</x:v>
-      </x:c>
-      <x:c r="J22" s="32" t="n">
-        <x:v>3.8000000000000003</x:v>
-      </x:c>
-      <x:c r="K22" s="32" t="n">
-        <x:f>IF(J22="","",(1/'Metadata'!$B$5)^(J22-1))</x:f>
-        <x:v>630.9573444801937</x:v>
-      </x:c>
-      <x:c r="L22" s="31" t="n">
-        <x:f>IF(E22=0,"",E22*K22)</x:f>
+        <x:f>IF(B22=0,"",B22*D22)</x:f>
         <x:v>1351.4144388960478</x:v>
       </x:c>
-      <x:c r="M22" s="31" t="n">
-        <x:f>IF(E22=0,"",I22-L22)</x:f>
-        <x:v>-1.5916157281026244e-12</x:v>
-      </x:c>
-      <x:c r="N22" s="32" t="n">
-        <x:f>IF(L22=0,"",I22/L22)</x:f>
-        <x:v>0.9999999999999988</x:v>
-      </x:c>
-      <x:c r="O22" s="34" t="n">
-        <x:f>IF(L22=0,"",M22/L22)</x:f>
-        <x:v>-1.1777406562288869e-15</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G22">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O22">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc3321c9aafea4140"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R151f65b6c0eb4667"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11420,7 +10146,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -11519,7 +10245,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>22085853.631860103</x:v>
+        <x:v>19613595.78582249</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -11533,7 +10259,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>22085853.631860096</x:v>
+        <x:v>21138321.64229359</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -11547,7 +10273,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>3.725290298461914e-9</x:v>
+        <x:v>-2472257.8460376114</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -11561,7 +10287,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>-3.725290298461914e-9</x:v>
+        <x:v>-947531.9895665087</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -11572,9 +10298,9 @@
         <x:v>EEZ_768</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -11586,47 +10312,19 @@
         <x:v>EEZ_768</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_768</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_768</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R71d3c380aa6f45bb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7ff8d70aba404c6f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11673,7 +10371,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
